--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2300,6 +2300,302 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129145289</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80139</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nargöl NV, Nargöl NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521077</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6439888</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På ask, flera bålar.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129145168</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80139</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nargöl NV, Nargöl NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521058</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6439882</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129145253</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95976</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nargöl NV, Nargöl NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>521077</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6439888</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>95976</v>
+        <v>95981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2305,7 +2305,7 @@
         <v>129145289</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129145168</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>95981</v>
+        <v>95984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2305,7 +2305,7 @@
         <v>129145289</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129145168</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>95984</v>
+        <v>95994</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2305,7 +2305,7 @@
         <v>129145289</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129145168</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96001</v>
+        <v>96003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96003</v>
+        <v>96029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96029</v>
+        <v>96030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96030</v>
+        <v>96031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2305,7 +2305,7 @@
         <v>129145289</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129145168</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96031</v>
+        <v>96035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2305,7 +2305,7 @@
         <v>129145289</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129145168</v>
       </c>
       <c r="B17" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96035</v>
+        <v>96037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96037</v>
+        <v>96041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96041</v>
+        <v>96049</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96049</v>
+        <v>96052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -2305,7 +2305,7 @@
         <v>129145289</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129145168</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>129145253</v>
       </c>
       <c r="B18" t="n">
-        <v>96052</v>
+        <v>96081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2596,6 +2596,491 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132311627</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521240</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6439828</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132311625</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106126</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>521092</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6439906</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132311623</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521535</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6439688</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132311624</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>521509</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6439714</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132311572</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>521600</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6439650</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>209508</v>
+        <v>6741711</v>
       </c>
       <c r="B2" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NARGÖL, 150 M S. GÅRDEN, Ög</t>
+          <t>250 M NV NARGÖL (07F8e11), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521611.0721824809</v>
+        <v>521409</v>
       </c>
       <c r="R2" t="n">
-        <v>6439401.289626284</v>
+        <v>6439710</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +743,14 @@
           <t>2000-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-07-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Grova ädellövträd</t>
+          <t>070584111 / CLI CORR / Enstaka-sparsam (1)  / OBJ.AREA:0,4 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,69 +761,85 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ädellövskog /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Jens Johannesson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Jens Johannesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1894880</v>
+        <v>115319206</v>
       </c>
       <c r="B3" t="n">
-        <v>76861</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>721</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Grifola frondosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Dicks.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NARGÖL, 150 M S. GÅRDEN, Ög</t>
+          <t>SV Skarfall, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521611.0721824809</v>
+        <v>521357</v>
       </c>
       <c r="R3" t="n">
-        <v>6439401.289626284</v>
+        <v>6439908</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,35 +863,26 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-07-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Grova ädellövträd</t>
+          <t>Fjolårets exemplar men högst sannolikt en korallticka på denna mycket grova, gamla vidgreniga ek.</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,53 +901,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2012718</v>
+        <v>115319262</v>
       </c>
       <c r="B4" t="n">
-        <v>73506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>1114</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NARGÖL, 150 M S. GÅRDEN, Ög</t>
+          <t>SV Skarfall, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521611.0721824809</v>
+        <v>521357</v>
       </c>
       <c r="R4" t="n">
-        <v>6439401.289626284</v>
+        <v>6439908</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +973,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-07-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Grova ädellövträd</t>
+          <t>Dessa exemplar likar den lav som tidigare namngavs blyertslav men enligt tidigare rapporter finns även "verklig" gammelekslav någonstans vid Nargöl.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,57 +1011,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83213681</v>
+        <v>129145253</v>
       </c>
       <c r="B5" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Naregöl, Ög</t>
+          <t>Nargöl NV, Nargöl NV, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521732.672348888</v>
+        <v>521077</v>
       </c>
       <c r="R5" t="n">
-        <v>6439341.692433155</v>
+        <v>6439888</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,29 +1074,14 @@
           <t>Ulrika</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5B169B23-C3B7-49B7-8F2E-BE2CE62DFC1A</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,70 +1096,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83214064</v>
+        <v>579720</v>
       </c>
       <c r="B6" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Naregöl, Ög</t>
+          <t>250 M. SO NARGÖL (07F8e07), Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520990.7794983133</v>
+        <v>521718</v>
       </c>
       <c r="R6" t="n">
-        <v>6439831.387212186</v>
+        <v>6439314</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1223,29 +1171,19 @@
           <t>Ulrika</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>A94AA8E9-B340-400F-9580-BB54F13BA502</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>070584071 / ANTI CUR / Tämligen allmän (2)  / OBJ.AREA:0,6 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,77 +1194,78 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Mossblock</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83213686</v>
+        <v>1082230</v>
       </c>
       <c r="B7" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223246</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521751.7977618555</v>
+        <v>521602</v>
       </c>
       <c r="R7" t="n">
-        <v>6439330.69640252</v>
+        <v>6439459</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,29 +1287,19 @@
           <t>Ulrika</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>B995DC71-93B3-4CE6-B12D-A34EE416CCD0</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-09-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventering skyddsvärda träd, Linköpings kommun</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,71 +1314,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13752421</v>
+        <v>115285408</v>
       </c>
       <c r="B8" t="n">
-        <v>9492</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101479</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>fallfälla</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nargöl, Ög</t>
+          <t>Naregöl, Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521527.4733198049</v>
+        <v>521610</v>
       </c>
       <c r="R8" t="n">
-        <v>6439680.978409946</v>
+        <v>6439616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,27 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2005-08-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2005-08-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fallfälla med (R)-(+)-gamma-decalactone</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,77 +1407,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Ek</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94911822</v>
+        <v>115317461</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grova lövträd V om Skarfall, Ulrika kyrka, Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521083.1973240901</v>
+        <v>521483</v>
       </c>
       <c r="R9" t="n">
-        <v>6439878.386352818</v>
+        <v>6439808</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,27 +1488,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>några ex relativt högt upp på några av träden, både asp och ask</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,38 +1502,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
-        </is>
-      </c>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94911771</v>
+        <v>132311572</v>
       </c>
       <c r="B10" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,49 +1531,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NV Nargöl, Ulrika kyrka, Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521057.0913913371</v>
+        <v>521600</v>
       </c>
       <c r="R10" t="n">
-        <v>6439808.482255958</v>
+        <v>6439650</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,27 +1585,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>i fuktig skog nordväst om Nargöl</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,38 +1599,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
-        </is>
-      </c>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115286207</v>
+        <v>132311619</v>
       </c>
       <c r="B11" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,37 +1628,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>2671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>300 M S.V. SKARFALL (300 M S.V. SKARFALL), Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521210</v>
+        <v>521561</v>
       </c>
       <c r="R11" t="n">
-        <v>6439947</v>
+        <v>6439725</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,17 +1682,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lönn</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,27 +1702,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115285400</v>
+        <v>132311621</v>
       </c>
       <c r="B12" t="n">
-        <v>93952</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,37 +1725,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Naregöl (Naregöl), Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521610</v>
+        <v>521549</v>
       </c>
       <c r="R12" t="n">
-        <v>6439616</v>
+        <v>6439692</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,12 +1779,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,27 +1799,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115285408</v>
+        <v>132311622</v>
       </c>
       <c r="B13" t="n">
-        <v>94147</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,17 +1842,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Naregöl (Naregöl), Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521610</v>
+        <v>521551</v>
       </c>
       <c r="R13" t="n">
-        <v>6439616</v>
+        <v>6439694</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2066,12 +1876,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,27 +1896,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115317445</v>
+        <v>132311623</v>
       </c>
       <c r="B14" t="n">
-        <v>90885</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2138,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521429</v>
+        <v>521535</v>
       </c>
       <c r="R14" t="n">
-        <v>6439734</v>
+        <v>6439688</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2168,12 +1973,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,15 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115317446</v>
+        <v>132311624</v>
       </c>
       <c r="B15" t="n">
-        <v>90885</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2240,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521568</v>
+        <v>521509</v>
       </c>
       <c r="R15" t="n">
-        <v>6439637</v>
+        <v>6439714</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2270,12 +2070,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,48 +2102,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145289</v>
+        <v>132311627</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>96501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nargöl NV, Nargöl NV, Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521077</v>
+        <v>521240</v>
       </c>
       <c r="R16" t="n">
-        <v>6439888</v>
+        <v>6439828</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,17 +2167,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På ask, flera bålar.</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,57 +2187,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129145168</v>
+        <v>132311628</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>96501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nargöl NV, Nargöl NV, Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521058</v>
+        <v>521223</v>
       </c>
       <c r="R17" t="n">
-        <v>6439882</v>
+        <v>6439847</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2469,12 +2264,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,22 +2284,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129145253</v>
+        <v>132311634</v>
       </c>
       <c r="B18" t="n">
-        <v>96081</v>
+        <v>96501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,37 +2307,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nargöl NV, Nargöl NV, Ög</t>
+          <t>Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521077</v>
+        <v>521363</v>
       </c>
       <c r="R18" t="n">
-        <v>6439888</v>
+        <v>6439920</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2566,12 +2361,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,22 +2381,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132311627</v>
+        <v>132311636</v>
       </c>
       <c r="B19" t="n">
-        <v>96433</v>
+        <v>96501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521240</v>
+        <v>521414</v>
       </c>
       <c r="R19" t="n">
-        <v>6439828</v>
+        <v>6439909</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2695,10 +2490,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132311625</v>
+        <v>132311637</v>
       </c>
       <c r="B20" t="n">
-        <v>106165</v>
+        <v>96501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,21 +2501,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2730,10 +2525,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521092</v>
+        <v>521411</v>
       </c>
       <c r="R20" t="n">
-        <v>6439906</v>
+        <v>6439911</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2792,10 +2587,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132311623</v>
+        <v>115285400</v>
       </c>
       <c r="B21" t="n">
-        <v>96433</v>
+        <v>96231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,37 +2598,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Naregöl, Ög</t>
+          <t>Naregöl, Naregöl, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521535</v>
+        <v>521610</v>
       </c>
       <c r="R21" t="n">
-        <v>6439688</v>
+        <v>6439616</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2857,12 +2652,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,22 +2672,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132311624</v>
+        <v>132311633</v>
       </c>
       <c r="B22" t="n">
-        <v>96433</v>
+        <v>96306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,21 +2695,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2924,10 +2719,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521509</v>
+        <v>521360</v>
       </c>
       <c r="R22" t="n">
-        <v>6439714</v>
+        <v>6439883</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2986,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132311572</v>
+        <v>115317445</v>
       </c>
       <c r="B23" t="n">
-        <v>96433</v>
+        <v>92497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2997,21 +2792,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521600</v>
+        <v>521429</v>
       </c>
       <c r="R23" t="n">
-        <v>6439650</v>
+        <v>6439734</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3051,12 +2846,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,6 +2875,2828 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>115317446</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>521568</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6439637</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>115285107</v>
+      </c>
+      <c r="B25" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Naregöl, Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>521525</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6439671</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115319287</v>
+      </c>
+      <c r="B26" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SV Skarfall, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>521357</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6439908</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Grov ek och närliggande klenare ek.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2045717</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>521587</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6439531</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1998-09-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1998-09-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Inventering skyddsvärda träd, Linköpings kommun</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115318251</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>521565</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6439658</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132311631</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>521292</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6439816</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132311632</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521291</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6439826</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115286207</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>300 M S.V. SKARFALL, 300 M S.V. SKARFALL, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521210</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6439947</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Lönn</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>94911822</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grova lövträd V om Skarfall, Ulrika kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521084</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6439878</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>några ex relativt högt upp på några av träden, både asp och ask</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129145168</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nargöl NV, Nargöl NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>521058</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6439882</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129145289</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nargöl NV, Nargöl NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>521077</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6439888</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På ask, flera bålar.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124354299</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>521262</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6439881</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>590 53, Ulrika, Östergötlands län</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132311629</v>
+      </c>
+      <c r="B36" t="n">
+        <v>107690</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521267</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6439825</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>94911771</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NV Nargöl, Ulrika kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>521058</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6439808</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>i fuktig skog nordväst om Nargöl</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>83213681</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521733</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6439342</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>5B169B23-C3B7-49B7-8F2E-BE2CE62DFC1A</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2001-03-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2001-03-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>83214064</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>520991</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6439831</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A94AA8E9-B340-400F-9580-BB54F13BA502</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2001-03-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2001-03-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132311625</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>521092</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6439906</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4231740</v>
+      </c>
+      <c r="B41" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>250 M. SO NARGÖL (07F8e07), Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>521718</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6439314</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>070584071 / VIOL MIR / Enstaka-sparsam (1)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4920092</v>
+      </c>
+      <c r="B42" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>250 M. SO NARGÖL (07F8e07), Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>521718</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6439314</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>070584071 / DAPH MEZ / Tämligen allmän (2)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132311615</v>
+      </c>
+      <c r="B43" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>521627</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6439695</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132311630</v>
+      </c>
+      <c r="B44" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>521270</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6439820</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132658537</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skarfall, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>521350</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6440055</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>William Rosén, Emil Ideskär, Tilde Tängerstad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115317467</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>521483</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6439808</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5259331</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>250 M. SO NARGÖL (07F8e07), Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>521718</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6439314</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>070584071 / ACTA SPI / Allmän-riklig (3)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>83213686</v>
+      </c>
+      <c r="B48" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Naregöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>521752</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6439331</v>
+      </c>
+      <c r="S48" t="n">
+        <v>50</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B995DC71-93B3-4CE6-B12D-A34EE416CCD0</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2001-03-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2001-03-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6686695</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>250 M NV NARGÖL (07F8e11), Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>521409</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6439710</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2000-07-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>070584111 / PEL COLL / Enstaka-sparsam (1)  / OBJ.AREA:0,4 ha</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Ädellövskog /</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Gammal skogslind</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>115286115</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>300 M S.V. SKARFALL, 300 M S.V. SKARFALL, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>521183</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6439938</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På lönn</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60643-2024 artfynd.xlsx
+++ b/artfynd/A 60643-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115319206</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115319262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145253</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/579720</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1082230</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285408</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115317461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311572</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311619</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311621</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311622</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311623</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311624</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311627</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311628</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2390,6 +2475,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311634</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2487,6 +2577,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311636</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2584,6 +2679,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311637</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2681,6 +2781,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285400</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2778,6 +2883,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311633</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2875,6 +2985,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115317445</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2972,6 +3087,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115317446</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3069,6 +3189,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285107</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3175,6 +3300,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115319287</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3277,6 +3407,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2045717</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3378,6 +3513,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115318251</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3475,6 +3615,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311631</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3572,6 +3717,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311632</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3674,6 +3824,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115286207</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3784,6 +3939,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94911822</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3881,6 +4041,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145168</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3983,6 +4148,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145289</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4085,6 +4255,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124354299</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4183,6 +4358,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311629</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4302,6 +4482,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94911771</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4412,6 +4597,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83213681</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4522,6 +4712,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83214064</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4619,6 +4814,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311625</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4730,6 +4930,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4231740</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4841,6 +5046,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4920092</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4938,6 +5148,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311615</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5035,6 +5250,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132311630</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5161,6 +5381,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132658537</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5258,6 +5483,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115317467</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5369,6 +5599,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5259331</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5479,6 +5714,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83213686</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5595,6 +5835,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6686695</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5697,8 +5942,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115286115</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>